--- a/data/trans_camb/IP2004-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP2004-Edad-trans_camb.xlsx
@@ -677,17 +677,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,49; 0,0</t>
+          <t>-4,25; 0,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,67; 0,0</t>
+          <t>-4,27; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,23; 0,0</t>
+          <t>-4,79; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -707,17 +707,17 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,3; 0,0</t>
+          <t>-1,93; 0,0</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,3; 0,0</t>
+          <t>-1,94; 0,0</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-2,2; 0,0</t>
+          <t>-1,94; 0,0</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 3,44</t>
+          <t>-0,45; 3,14</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 1,98</t>
+          <t>-1,36; 1,9</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,41; -0,26</t>
+          <t>-2,49; -0,27</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,55; 1,59</t>
+          <t>-1,49; 1,47</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,7; -0,26</t>
+          <t>-2,38; -0,26</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 4,46</t>
+          <t>-0,4; 4,44</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 1,76</t>
+          <t>-0,69; 1,81</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,35; 0,38</t>
+          <t>-1,56; 0,28</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 1,92</t>
+          <t>-0,88; 1,78</t>
         </is>
       </c>
     </row>
@@ -999,7 +999,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-44,73; 1111,05</t>
+          <t>-50,46; 1023,24</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1014,32 +1014,32 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
+          <t>-100,0; 530,08</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-55,06; 1277,58</t>
+          <t>-51,3; 1263,04</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-47,4; 324,07</t>
+          <t>-54,25; 332,17</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 210,68</t>
+          <t>-100,0; 110,22</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-67,4; 343,7</t>
+          <t>-71,4; 331,67</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-6,03; 0,98</t>
+          <t>-6,28; 0,95</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,95; 4,01</t>
+          <t>-4,15; 3,76</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,52; 0,21</t>
+          <t>-6,85; 0,44</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,6; 2,31</t>
+          <t>-5,8; 2,1</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-7,38; -0,22</t>
+          <t>-7,31; -0,18</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-7,19; 0,08</t>
+          <t>-7,15; -0,19</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-4,95; 0,46</t>
+          <t>-4,92; 0,59</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-4,27; 1,04</t>
+          <t>-4,56; 0,89</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-5,68; -0,8</t>
+          <t>-5,82; -0,8</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-83,62; 48,25</t>
+          <t>-85,03; 59,45</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-57,66; 155,41</t>
+          <t>-57,85; 151,31</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-90,01; 24,51</t>
+          <t>-89,21; 39,48</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-73,42; 77,84</t>
+          <t>-75,05; 73,6</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-88,66; 14,61</t>
+          <t>-87,55; 6,2</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-86,21; 23,75</t>
+          <t>-87,37; 19,67</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-69,51; 17,04</t>
+          <t>-72,54; 19,05</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-62,02; 32,46</t>
+          <t>-64,26; 30,74</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-82,03; -10,3</t>
+          <t>-81,87; -15,96</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,03; 5,09</t>
+          <t>-3,72; 5,03</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-6,24; 2,04</t>
+          <t>-6,11; 1,8</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-8,86; -2,22</t>
+          <t>-8,56; -2,2</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,36; 3,18</t>
+          <t>-4,29; 3,14</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-4,89; 2,53</t>
+          <t>-4,96; 2,07</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-6,15; -0,14</t>
+          <t>-6,33; -0,23</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-3,24; 2,48</t>
+          <t>-3,12; 2,52</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-4,46; 0,81</t>
+          <t>-4,43; 1,08</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-6,37; -1,87</t>
+          <t>-6,73; -2,1</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-46,36; 119,53</t>
+          <t>-44,82; 116,73</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-73,06; 52,61</t>
+          <t>-72,28; 39,42</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-93,18; -43,23</t>
+          <t>-92,2; -41,21</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-59,33; 97,39</t>
+          <t>-60,4; 97,73</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-66,46; 77,47</t>
+          <t>-68,63; 57,3</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-79,04; 7,03</t>
+          <t>-81,17; -0,1</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-43,7; 49,47</t>
+          <t>-42,04; 51,53</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-60,04; 18,14</t>
+          <t>-57,59; 26,93</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-81,56; -37,83</t>
+          <t>-82,34; -35,74</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 1,34</t>
+          <t>-1,89; 1,33</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,29; 0,97</t>
+          <t>-2,12; 1,02</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-3,89; -1,07</t>
+          <t>-3,59; -0,87</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 0,8</t>
+          <t>-2,18; 0,84</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-2,88; -0,39</t>
+          <t>-2,85; -0,28</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-2,26; 0,51</t>
+          <t>-2,38; 0,51</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-1,61; 0,5</t>
+          <t>-1,66; 0,59</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-2,06; -0,02</t>
+          <t>-2,1; -0,15</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-2,53; -0,55</t>
+          <t>-2,69; -0,56</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-43,6; 50,94</t>
+          <t>-45,27; 48,72</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-51,94; 36,35</t>
+          <t>-49,18; 42,93</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-84,58; -29,27</t>
+          <t>-83,86; -28,78</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-54,11; 35,67</t>
+          <t>-55,97; 34,86</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-71,9; -9,91</t>
+          <t>-72,04; -6,62</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-57,81; 22,01</t>
+          <t>-60,09; 19,8</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-40,92; 20,62</t>
+          <t>-43,17; 20,96</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-54,62; 2,49</t>
+          <t>-54,02; -3,87</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-66,06; -17,16</t>
+          <t>-65,66; -19,61</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP2004-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP2004-Edad-trans_camb.xlsx
@@ -677,17 +677,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,25; 0,0</t>
+          <t>-4,82; 0,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,27; 0,0</t>
+          <t>-4,87; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,79; 0,0</t>
+          <t>-4,71; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -707,7 +707,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,93; 0,0</t>
+          <t>-1,94; 0,0</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 3,14</t>
+          <t>-0,33; 3,58</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 1,9</t>
+          <t>-1,43; 1,75</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,49; -0,27</t>
+          <t>-2,26; -0,26</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 1,47</t>
+          <t>-1,5; 1,43</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,38; -0,26</t>
+          <t>-2,63; -0,27</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 4,44</t>
+          <t>-0,48; 4,25</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 1,81</t>
+          <t>-0,55; 1,83</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 0,28</t>
+          <t>-1,49; 0,27</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 1,78</t>
+          <t>-0,73; 1,81</t>
         </is>
       </c>
     </row>
@@ -999,7 +999,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-50,46; 1023,24</t>
+          <t>-60,42; 913,78</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 530,08</t>
+          <t>-100,0; 523,24</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1024,22 +1024,22 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-51,3; 1263,04</t>
+          <t>-54,91; 891,57</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-54,25; 332,17</t>
+          <t>-44,94; 323,39</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 110,22</t>
+          <t>-100,0; 99,96</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-71,4; 331,67</t>
+          <t>-64,35; 339,7</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-6,28; 0,95</t>
+          <t>-6,01; 1,12</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,15; 3,76</t>
+          <t>-3,98; 3,71</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,85; 0,44</t>
+          <t>-6,2; 0,34</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,8; 2,1</t>
+          <t>-5,77; 2,08</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-7,31; -0,18</t>
+          <t>-7,16; -0,18</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-7,15; -0,19</t>
+          <t>-6,98; -0,25</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-4,92; 0,59</t>
+          <t>-4,8; 0,39</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-4,56; 0,89</t>
+          <t>-4,63; 0,56</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-5,82; -0,8</t>
+          <t>-5,77; -0,71</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-85,03; 59,45</t>
+          <t>-85,01; 60,44</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-57,85; 151,31</t>
+          <t>-58,0; 158,87</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-89,21; 39,48</t>
+          <t>-89,11; 60,47</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-75,05; 73,6</t>
+          <t>-77,84; 55,17</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-87,55; 6,2</t>
+          <t>-88,05; 3,07</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-87,37; 19,67</t>
+          <t>-86,77; 1,15</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-72,54; 19,05</t>
+          <t>-72,29; 12,76</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-64,26; 30,74</t>
+          <t>-65,06; 19,24</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-81,87; -15,96</t>
+          <t>-82,45; -10,56</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,72; 5,03</t>
+          <t>-4,03; 4,72</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-6,11; 1,8</t>
+          <t>-6,28; 1,71</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-8,56; -2,2</t>
+          <t>-8,75; -2,09</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,29; 3,14</t>
+          <t>-4,14; 3,43</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-4,96; 2,07</t>
+          <t>-4,77; 2,21</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-6,33; -0,23</t>
+          <t>-6,18; -0,01</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-3,12; 2,52</t>
+          <t>-3,07; 2,36</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-4,43; 1,08</t>
+          <t>-4,29; 0,95</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-6,73; -2,1</t>
+          <t>-6,45; -1,99</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-44,82; 116,73</t>
+          <t>-49,51; 102,47</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-72,28; 39,42</t>
+          <t>-69,47; 47,16</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-92,2; -41,21</t>
+          <t>-92,4; -36,55</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-60,4; 97,73</t>
+          <t>-61,74; 94,33</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-68,63; 57,3</t>
+          <t>-67,36; 56,92</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-81,17; -0,1</t>
+          <t>-82,16; 10,02</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-42,04; 51,53</t>
+          <t>-40,66; 50,51</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-57,59; 26,93</t>
+          <t>-57,47; 24,97</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-82,34; -35,74</t>
+          <t>-82,1; -37,91</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 1,33</t>
+          <t>-1,83; 1,52</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,12; 1,02</t>
+          <t>-2,33; 0,93</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-3,59; -0,87</t>
+          <t>-3,58; -0,88</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,18; 0,84</t>
+          <t>-2,24; 0,89</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-2,85; -0,28</t>
+          <t>-2,89; -0,22</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-2,38; 0,51</t>
+          <t>-2,32; 0,59</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 0,59</t>
+          <t>-1,58; 0,64</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-2,1; -0,15</t>
+          <t>-2,18; -0,06</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-2,69; -0,56</t>
+          <t>-2,57; -0,53</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-45,27; 48,72</t>
+          <t>-43,62; 62,47</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-49,18; 42,93</t>
+          <t>-52,41; 35,3</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-83,86; -28,78</t>
+          <t>-83,07; -26,95</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-55,97; 34,86</t>
+          <t>-57,38; 38,24</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-72,04; -6,62</t>
+          <t>-73,01; -4,54</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-60,09; 19,8</t>
+          <t>-59,35; 26,08</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-43,17; 20,96</t>
+          <t>-40,86; 23,97</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-54,02; -3,87</t>
+          <t>-54,36; -0,63</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-65,66; -19,61</t>
+          <t>-66,2; -18,78</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP2004-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP2004-Edad-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>-0,84</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>-0,84</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>-0,84</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,82; 0,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,87; 0,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,71; 0,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-4,49; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-4,67; 0,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-5,23; 0,0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 0,0</t>
+          <t>-2,3; 0,0</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 0,0</t>
+          <t>-2,3; 0,0</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 0,0</t>
+          <t>-2,2; 0,0</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -840,34 +840,34 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-0,08</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-1,04</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1,61</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>1,24</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>-0,04</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>-0,96</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-0,08</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-1,04</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>1,47</t>
-        </is>
-      </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
           <t>0,54</t>
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,34</t>
+          <t>0,37</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 3,58</t>
+          <t>-1,55; 1,59</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,43; 1,75</t>
+          <t>-2,7; -0,26</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,26; -0,26</t>
+          <t>-0,45; 4,76</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 1,43</t>
+          <t>-0,38; 3,44</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,63; -0,27</t>
+          <t>-1,5; 1,98</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 4,25</t>
+          <t>-2,41; -0,26</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 1,83</t>
+          <t>-0,54; 1,76</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 0,27</t>
+          <t>-1,35; 0,38</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 1,81</t>
+          <t>-0,79; 2,03</t>
         </is>
       </c>
     </row>
@@ -946,34 +946,34 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-7,44%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>153,81%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>129,44%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>-4,05%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-7,44%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>140,99%</t>
-        </is>
-      </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
           <t>54,19%</t>
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>33,78%</t>
+          <t>37,33%</t>
         </is>
       </c>
     </row>
@@ -999,7 +999,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-60,42; 913,78</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1009,37 +1009,37 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
+          <t>-51,14; 1376,65</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>-44,73; 1111,05</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 523,24</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-54,91; 891,57</t>
-        </is>
-      </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-44,94; 323,39</t>
+          <t>-47,4; 324,07</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 99,96</t>
+          <t>-100,0; 210,68</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-64,35; 339,7</t>
+          <t>-70,1; 350,06</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-1,68</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-3,3</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>-3,17</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>-2,17</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>-0,01</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-2,84</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-1,68</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-3,3</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-3,2</t>
+          <t>-2,8</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-3,01</t>
+          <t>-2,99</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-6,01; 1,12</t>
+          <t>-5,6; 2,31</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,98; 3,71</t>
+          <t>-7,38; -0,22</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,2; 0,34</t>
+          <t>-7,19; 0,23</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,77; 2,08</t>
+          <t>-6,03; 0,98</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-7,16; -0,18</t>
+          <t>-3,95; 4,01</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-6,98; -0,25</t>
+          <t>-6,56; 0,32</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-4,8; 0,39</t>
+          <t>-4,95; 0,46</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-4,63; 0,56</t>
+          <t>-4,27; 1,04</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-5,77; -0,71</t>
+          <t>-5,65; -0,76</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-30,59%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-59,97%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>-57,63%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>-45,99%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>-0,2%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-60,28%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-30,59%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-59,97%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-58,16%</t>
+          <t>-59,43%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-58,85%</t>
+          <t>-58,32%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-85,01; 60,44</t>
+          <t>-73,42; 77,84</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-58,0; 158,87</t>
+          <t>-88,66; 14,61</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-89,11; 60,47</t>
+          <t>-85,99; 27,05</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-77,84; 55,17</t>
+          <t>-83,62; 48,25</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-88,05; 3,07</t>
+          <t>-57,66; 155,41</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-86,77; 1,15</t>
+          <t>-90,18; 26,57</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-72,29; 12,76</t>
+          <t>-69,51; 17,04</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-65,06; 19,24</t>
+          <t>-62,02; 32,46</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-82,45; -10,56</t>
+          <t>-82,29; -9,45</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-0,79</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-1,33</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>-3,19</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>0,16</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>-2,22</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-5,13</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-0,79</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-1,33</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-3,03</t>
+          <t>-4,93</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-4,04</t>
+          <t>-4,03</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,03; 4,72</t>
+          <t>-4,36; 3,18</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-6,28; 1,71</t>
+          <t>-4,89; 2,53</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-8,75; -2,09</t>
+          <t>-6,34; -0,45</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,14; 3,43</t>
+          <t>-4,03; 5,09</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-4,77; 2,21</t>
+          <t>-6,24; 2,04</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-6,18; -0,01</t>
+          <t>-8,71; -2,0</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-3,07; 2,36</t>
+          <t>-3,24; 2,48</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-4,29; 0,95</t>
+          <t>-4,46; 0,81</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-6,45; -1,99</t>
+          <t>-6,21; -1,85</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-14,37%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-24,03%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>-57,85%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>2,34%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>-32,96%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-76,23%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-14,37%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-24,03%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-54,94%</t>
+          <t>-73,29%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-66,17%</t>
+          <t>-65,96%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-49,51; 102,47</t>
+          <t>-59,33; 97,39</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-69,47; 47,16</t>
+          <t>-66,46; 77,47</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-92,4; -36,55</t>
+          <t>-81,13; -0,09</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-61,74; 94,33</t>
+          <t>-46,36; 119,53</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-67,36; 56,92</t>
+          <t>-73,06; 52,61</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-82,16; 10,02</t>
+          <t>-91,69; -34,71</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-40,66; 50,51</t>
+          <t>-43,7; 49,47</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-57,47; 24,97</t>
+          <t>-60,04; 18,14</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-82,1; -37,91</t>
+          <t>-80,38; -35,47</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>-0,73</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-1,53</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>-0,9</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>-0,26</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>-0,61</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-2,26</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>-0,73</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>-1,53</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-0,88</t>
+          <t>-2,15</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-1,53</t>
+          <t>-1,49</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 1,52</t>
+          <t>-2,1; 0,8</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,33; 0,93</t>
+          <t>-2,88; -0,39</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-3,58; -0,88</t>
+          <t>-2,27; 0,46</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,24; 0,89</t>
+          <t>-1,85; 1,34</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-2,89; -0,22</t>
+          <t>-2,29; 0,97</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-2,32; 0,59</t>
+          <t>-3,76; -0,88</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 0,64</t>
+          <t>-1,61; 0,5</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-2,18; -0,06</t>
+          <t>-2,06; -0,02</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-2,57; -0,53</t>
+          <t>-2,47; -0,46</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>-22,98%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-48,4%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>-28,37%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>-7,7%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>-17,67%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-65,99%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>-22,98%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>-48,4%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-27,92%</t>
+          <t>-62,62%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-46,55%</t>
+          <t>-45,34%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-43,62; 62,47</t>
+          <t>-54,11; 35,67</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-52,41; 35,3</t>
+          <t>-71,9; -9,91</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-83,07; -26,95</t>
+          <t>-57,99; 19,65</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-57,38; 38,24</t>
+          <t>-43,6; 50,94</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-73,01; -4,54</t>
+          <t>-51,94; 36,35</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-59,35; 26,08</t>
+          <t>-83,11; -18,52</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-40,86; 23,97</t>
+          <t>-40,92; 20,62</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-54,36; -0,63</t>
+          <t>-54,62; 2,49</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-66,2; -18,78</t>
+          <t>-64,98; -14,68</t>
         </is>
       </c>
     </row>
